--- a/docs/sverka-s-tablicami.xlsx
+++ b/docs/sverka-s-tablicami.xlsx
@@ -543,7 +543,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
@@ -9488,22 +9488,26 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>Сельскохозяйственная спецтехника</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Прицепная и навесная сельхозтехника (плуги, сеялки, опрыскиватели)</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>НЕТ В МАКЕТЕ</t>
-        </is>
-      </c>
-      <c r="D29" s="3" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>есть</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>вид техники</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -9677,7 +9681,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Тип ТС; Тип агрегатирования; Тип двигателя</t>
+          <t>Тип ТС; Вид техники; Тип агрегатирования; Тип двигателя</t>
         </is>
       </c>
     </row>
